--- a/02_Output/G-Form/Summary_results/Table_population_effects_summary.xlsx
+++ b/02_Output/G-Form/Summary_results/Table_population_effects_summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t xml:space="preserve">Exposure and scenario</t>
   </si>
@@ -210,6 +210,27 @@
   </si>
   <si>
     <t xml:space="preserve">-2.97 (-5.25; -0.47)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 10 ppbv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17 (5.97; 9.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51209 (42609; 67335)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0480 (1.0033; 1.0926)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33 (0.02; 0.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.33 (-0.63; -0.02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.80 (-9.28; -0.31)</t>
   </si>
   <si>
     <t xml:space="preserve">&lt; 5 ppbv</t>
@@ -955,94 +976,117 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
+      <c r="B15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>13</v>
+      <c r="A16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>87</v>
+      <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/02_Output/G-Form/Summary_results/Table_population_effects_summary.xlsx
+++ b/02_Output/G-Form/Summary_results/Table_population_effects_summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t xml:space="preserve">Exposure and scenario</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">48863 (40082; 66307)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0000 (1.0000; 1.0000)</t>
+    <t xml:space="preserve">1.000 (1.000; 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">0.00 (0.00; 0.00)</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">49226 (40033; 65118)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0074 (0.9885; 1.0270)</t>
+    <t xml:space="preserve">1.007 (0.988; 1.027)</t>
   </si>
   <si>
     <t xml:space="preserve">0.05 (-0.09; 0.19)</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">49394 (39593; 65204)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0109 (0.9815; 1.0390)</t>
+    <t xml:space="preserve">1.011 (0.981; 1.039)</t>
   </si>
   <si>
     <t xml:space="preserve">0.07 (-0.14; 0.27)</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">49620 (40041; 65493)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0155 (0.9735; 1.0564)</t>
+    <t xml:space="preserve">1.015 (0.973; 1.056)</t>
   </si>
   <si>
     <t xml:space="preserve">0.11 (-0.20; 0.38)</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">49857 (40802; 64649)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0203 (0.9664; 1.0646)</t>
+    <t xml:space="preserve">1.020 (0.966; 1.065)</t>
   </si>
   <si>
     <t xml:space="preserve">0.14 (-0.27; 0.46)</t>
@@ -140,6 +140,27 @@
     <t xml:space="preserve">-2.03 (-6.46; 3.36)</t>
   </si>
   <si>
+    <t xml:space="preserve">Reduced by 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86 (5.59; 8.93)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48984 (39914; 63744)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.002 (0.996; 1.008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (-0.03; 0.05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02 (-0.05; 0.03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.25 (-0.77; 0.43)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reduced by 20%</t>
   </si>
   <si>
@@ -149,7 +170,7 @@
     <t xml:space="preserve">49106 (40136; 63845)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0050 (0.9915; 1.0155)</t>
+    <t xml:space="preserve">1.005 (0.992; 1.016)</t>
   </si>
   <si>
     <t xml:space="preserve">0.03 (-0.07; 0.11)</t>
@@ -161,6 +182,27 @@
     <t xml:space="preserve">-0.50 (-1.54; 0.85)</t>
   </si>
   <si>
+    <t xml:space="preserve">Reduced by 30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90 (5.64; 8.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49228 (40276; 64086)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.007 (0.987; 1.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (-0.10; 0.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.05 (-0.17; 0.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.75 (-2.33; 1.28)</t>
+  </si>
+  <si>
     <t xml:space="preserve">NO2 (ppbv)</t>
   </si>
   <si>
@@ -179,7 +221,7 @@
     <t xml:space="preserve">49707 (41254; 66192)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0173 (1.0008; 1.0313)</t>
+    <t xml:space="preserve">1.017 (1.001; 1.031)</t>
   </si>
   <si>
     <t xml:space="preserve">0.12 (0.01; 0.21)</t>
@@ -200,7 +242,7 @@
     <t xml:space="preserve">50315 (40038; 66254)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0297 (1.0047; 1.0525)</t>
+    <t xml:space="preserve">1.030 (1.005; 1.052)</t>
   </si>
   <si>
     <t xml:space="preserve">0.20 (0.04; 0.38)</t>
@@ -221,7 +263,7 @@
     <t xml:space="preserve">51209 (42609; 67335)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0480 (1.0033; 1.0926)</t>
+    <t xml:space="preserve">1.048 (1.003; 1.093)</t>
   </si>
   <si>
     <t xml:space="preserve">0.33 (0.02; 0.63)</t>
@@ -242,7 +284,7 @@
     <t xml:space="preserve">52273 (43851; 68359)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0698 (1.0045; 1.1290)</t>
+    <t xml:space="preserve">1.070 (1.004; 1.129)</t>
   </si>
   <si>
     <t xml:space="preserve">0.48 (0.03; 0.86)</t>
@@ -254,13 +296,31 @@
     <t xml:space="preserve">-6.98 (-12.90; -0.45)</t>
   </si>
   <si>
+    <t xml:space="preserve">6.90 (5.72; 9.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49294 (40832; 65934)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.009 (1.000; 1.016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 (0.00; 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.06 (-0.11; -0.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.88 (-1.59; -0.02)</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.97 (5.51; 9.19)</t>
   </si>
   <si>
     <t xml:space="preserve">49728 (39341; 65585)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0177 (1.0023; 1.0310)</t>
+    <t xml:space="preserve">1.018 (1.002; 1.031)</t>
   </si>
   <si>
     <t xml:space="preserve">0.12 (0.02; 0.22)</t>
@@ -272,6 +332,24 @@
     <t xml:space="preserve">-1.77 (-3.10; -0.23)</t>
   </si>
   <si>
+    <t xml:space="preserve">7.03 (5.86; 9.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50167 (41819; 66473)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.027 (1.001; 1.049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18 (0.01; 0.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.18 (-0.32; -0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.67 (-4.85; -0.09)</t>
+  </si>
+  <si>
     <t xml:space="preserve">O3 (ppbv)</t>
   </si>
   <si>
@@ -281,13 +359,31 @@
     <t xml:space="preserve">48863 (38986; 62453)</t>
   </si>
   <si>
+    <t xml:space="preserve">6.71 (5.37; 8.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47924 (38362; 60838)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.981 (0.971; 0.990)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.13 (-0.23; -0.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13 (0.06; 0.23)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92 (1.01; 2.88)</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.58 (5.29; 8.36)</t>
   </si>
   <si>
     <t xml:space="preserve">47005 (37779; 59662)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9620 (0.9433; 0.9799)</t>
+    <t xml:space="preserve">0.962 (0.943; 0.980)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.26 (-0.45; -0.13)</t>
@@ -297,6 +393,24 @@
   </si>
   <si>
     <t xml:space="preserve">3.80 (2.01; 5.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46 (5.09; 8.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46104 (36363; 58955)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.944 (0.919; 0.969)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.39 (-0.65; -0.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39 (0.18; 0.65)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65 (3.26; 8.11)</t>
   </si>
 </sst>
 </file>
@@ -860,95 +974,95 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>8</v>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>58</v>
+      <c r="A11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -999,94 +1113,232 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>8</v>
+      <c r="A16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>94</v>
+      <c r="B22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
